--- a/Pestaña-Datos-2026.xlsx
+++ b/Pestaña-Datos-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1d86eecf8daf4f0d/Documents/SQL Server Management Studio 22/Tienda-sqlserver/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{A21CE433-5220-4B3A-AD58-F26396C2A12B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{956B819D-BA51-486F-BCA5-34B04A725FD9}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="8_{A21CE433-5220-4B3A-AD58-F26396C2A12B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B068501F-9D57-4A12-86E9-0A40F1018F06}"/>
   <bookViews>
-    <workbookView xWindow="-36" yWindow="60" windowWidth="11784" windowHeight="12264" xr2:uid="{638C54D4-C6BD-4367-9E1B-9832D4FF1947}"/>
+    <workbookView xWindow="492" yWindow="216" windowWidth="11784" windowHeight="12240" firstSheet="1" activeTab="3" xr2:uid="{638C54D4-C6BD-4367-9E1B-9832D4FF1947}"/>
   </bookViews>
   <sheets>
     <sheet name="datos_ventas" sheetId="4" r:id="rId1"/>
@@ -19,6 +19,7 @@
     <sheet name="Herramientas" sheetId="3" r:id="rId4"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">datos_ventas[[#All],[Region]:[Mes]]</definedName>
     <definedName name="DatosExternos_1" localSheetId="0" hidden="1">datos_ventas!$A$4:$D$12</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -39,6 +40,40 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Edwin</author>
+  </authors>
+  <commentList>
+    <comment ref="C3" authorId="0" shapeId="0" xr:uid="{B5FB1C18-8073-4962-A943-3EC72AE249E4}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Edwin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Vendedor con Mayor  Potencial </t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/connections.xml><?xml version="1.0" encoding="utf-8"?>
 <connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16">
   <connection id="1" xr16:uid="{0CFD031D-B38F-4DF0-8120-5712AADA2936}" keepAlive="1" name="Consulta - datos_ventas" description="Conexión a la consulta 'datos_ventas' en el libro." type="5" refreshedVersion="8" background="1" saveData="1">
@@ -159,10 +194,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="165" formatCode="dd/mm/yyyy;@"/>
-    <numFmt numFmtId="166" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    <numFmt numFmtId="164" formatCode="dd/mm/yyyy;@"/>
+    <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -177,6 +212,19 @@
       <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -214,29 +262,35 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="7">
     <dxf>
-      <numFmt numFmtId="165" formatCode="dd/mm/yyyy;@"/>
+      <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="2" formatCode="0.00"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="dd/mm/yyyy;@"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -1412,10 +1466,10 @@
     <sortCondition descending="1" ref="C5:C12"/>
   </sortState>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{D452EA5B-420B-43BC-87C0-7D8884CE9535}" uniqueName="1" name="Vendedor" queryTableFieldId="1" dataDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{D13761F2-891D-43F3-9F86-EDCD4F4F3210}" uniqueName="2" name="Region" queryTableFieldId="2" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{A3A8269B-C638-4D0C-BF5E-F26921D53044}" uniqueName="3" name="Ventas" queryTableFieldId="3"/>
-    <tableColumn id="4" xr3:uid="{6E50DAC9-0876-48B7-AA42-B831AEDF829A}" uniqueName="4" name="Mes" queryTableFieldId="4" dataDxfId="3"/>
+    <tableColumn id="1" xr3:uid="{D452EA5B-420B-43BC-87C0-7D8884CE9535}" uniqueName="1" name="Vendedor" queryTableFieldId="1" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{D13761F2-891D-43F3-9F86-EDCD4F4F3210}" uniqueName="2" name="Region" queryTableFieldId="2" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{A3A8269B-C638-4D0C-BF5E-F26921D53044}" uniqueName="3" name="Ventas" queryTableFieldId="3" dataDxfId="0"/>
+    <tableColumn id="4" xr3:uid="{6E50DAC9-0876-48B7-AA42-B831AEDF829A}" uniqueName="4" name="Mes" queryTableFieldId="4" dataDxfId="4"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1425,7 +1479,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{94217D4A-6AF6-4A79-A30A-36B9B3B4D184}" name="Tabla2" displayName="Tabla2" ref="A1:E9" totalsRowShown="0">
   <autoFilter ref="A1:E9" xr:uid="{94217D4A-6AF6-4A79-A30A-36B9B3B4D184}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{DE2E701A-1386-41C7-87CB-7E416F4F0403}" name="Fecha" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{DE2E701A-1386-41C7-87CB-7E416F4F0403}" name="Fecha" dataDxfId="3"/>
     <tableColumn id="2" xr3:uid="{FB5FAE74-F9B9-43DB-866D-A44FC902CB51}" name="Ventas"/>
     <tableColumn id="3" xr3:uid="{E4E62F30-8204-450E-AD3B-033E6EF70279}" name="Previsión(Ventas)"/>
     <tableColumn id="4" xr3:uid="{758201EE-DF65-4EFD-A6C4-E16281FCEE61}" name="Límite de confianza inferior(Ventas)" dataDxfId="2"/>
@@ -1674,7 +1728,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D05E2C09-4F21-4625-B4FA-3003AA99332C}">
-  <dimension ref="A4:F17"/>
+  <dimension ref="A4:F19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.5" bestFit="1" customWidth="1"/>
@@ -1698,126 +1752,132 @@
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+      <c r="A5" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" t="s">
         <v>13</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="7">
         <v>25000</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+      <c r="A6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" t="s">
         <v>10</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="7">
         <v>22000</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
+      <c r="A7" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" t="s">
         <v>5</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="7">
         <v>18000</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
+      <c r="A8" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" t="s">
         <v>5</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="7">
         <v>15000</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
+      <c r="A9" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" t="s">
         <v>8</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="7">
         <v>9000</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
+      <c r="A10" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" t="s">
         <v>8</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="7">
         <v>8000</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
+      <c r="A11" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" t="s">
         <v>13</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="7">
         <v>5000</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D11" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
+      <c r="A12" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" t="s">
         <v>10</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="7">
         <v>3000</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D12" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="4:6" x14ac:dyDescent="0.25">
       <c r="F17">
         <v>6</v>
       </c>
     </row>
+    <row r="19" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D19" s="6"/>
+    </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="TgB+0FLDJot86FxysWk8oS9MFqoqRMnXkattsjBZDRPAy2hpGYjoFRqRG2NIfOeobsPgCZdoLS7I74VZ2w/4jA==" saltValue="QYHtVMEJhLGzyNQN9fu3yw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <printOptions headings="1" gridLines="1"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
@@ -1827,7 +1887,7 @@
   <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.19921875" style="5"/>
+    <col min="1" max="1" width="11.19921875" style="4"/>
     <col min="3" max="3" width="18.19921875" customWidth="1"/>
     <col min="4" max="4" width="33.69921875" customWidth="1"/>
     <col min="5" max="5" width="34.69921875" customWidth="1"/>
@@ -1835,7 +1895,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>20</v>
       </c>
       <c r="B1" t="s">
@@ -1852,7 +1912,7 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="5">
+      <c r="A2" s="4">
         <v>46023</v>
       </c>
       <c r="B2">
@@ -1860,7 +1920,7 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="5">
+      <c r="A3" s="4">
         <v>46054</v>
       </c>
       <c r="B3">
@@ -1868,7 +1928,7 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="5">
+      <c r="A4" s="4">
         <v>46082</v>
       </c>
       <c r="B4">
@@ -1876,7 +1936,7 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="5">
+      <c r="A5" s="4">
         <v>46113</v>
       </c>
       <c r="B5">
@@ -1884,7 +1944,7 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="5">
+      <c r="A6" s="4">
         <v>46143</v>
       </c>
       <c r="B6">
@@ -1892,35 +1952,35 @@
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="5">
+      <c r="A7" s="4">
         <v>46174</v>
       </c>
       <c r="B7">
         <v>188000</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="5">
         <v>188000</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D7" s="3">
         <v>188000</v>
       </c>
-      <c r="E7" s="4">
+      <c r="E7" s="3">
         <v>188000</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A8" s="5">
+      <c r="A8" s="4">
         <v>46204</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="5">
         <f>_xlfn.FORECAST.ETS(A8,$B$2:$B$7,$A$2:$A$7,1,1)</f>
         <v>207029.39498525765</v>
       </c>
-      <c r="D8" s="4">
+      <c r="D8" s="3">
         <f>C8-_xlfn.FORECAST.ETS.CONFINT(A8,$B$2:$B$7,$A$2:$A$7,0.95,1,1)</f>
         <v>176488.98219442804</v>
       </c>
-      <c r="E8" s="4">
+      <c r="E8" s="3">
         <f>C8+_xlfn.FORECAST.ETS.CONFINT(A8,$B$2:$B$7,$A$2:$A$7,0.95,1,1)</f>
         <v>237569.80777608725</v>
       </c>
@@ -1929,18 +1989,18 @@
       </c>
     </row>
     <row r="9" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A9" s="5">
+      <c r="A9" s="4">
         <v>46235</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="5">
         <f>_xlfn.FORECAST.ETS(A9,$B$2:$B$7,$A$2:$A$7,1,1)</f>
         <v>214940.37056875639</v>
       </c>
-      <c r="D9" s="4">
+      <c r="D9" s="3">
         <f>C9-_xlfn.FORECAST.ETS.CONFINT(A9,$B$2:$B$7,$A$2:$A$7,0.95,1,1)</f>
         <v>183452.6125444473</v>
       </c>
-      <c r="E9" s="4">
+      <c r="E9" s="3">
         <f>C9+_xlfn.FORECAST.ETS.CONFINT(A9,$B$2:$B$7,$A$2:$A$7,0.95,1,1)</f>
         <v>246428.12859306548</v>
       </c>
@@ -1972,7 +2032,7 @@
       </c>
     </row>
     <row r="3" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="3">
+      <c r="A3" s="2">
         <v>46023</v>
       </c>
       <c r="B3">
@@ -1980,7 +2040,7 @@
       </c>
     </row>
     <row r="4" spans="1:2" collapsed="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="3">
+      <c r="A4" s="2">
         <f>SUBTOTAL(9,A3:A3)</f>
         <v>46023</v>
       </c>
@@ -1990,7 +2050,7 @@
       </c>
     </row>
     <row r="5" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="3">
+      <c r="A5" s="2">
         <v>46054</v>
       </c>
       <c r="B5">
@@ -1998,7 +2058,7 @@
       </c>
     </row>
     <row r="6" spans="1:2" collapsed="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="3">
+      <c r="A6" s="2">
         <f>SUBTOTAL(9,A5:A5)</f>
         <v>46054</v>
       </c>
@@ -2008,7 +2068,7 @@
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="3">
+      <c r="A7" s="2">
         <v>46082</v>
       </c>
       <c r="B7">
@@ -2016,7 +2076,7 @@
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="3">
+      <c r="A8" s="2">
         <f>SUBTOTAL(9,A7:A7)</f>
         <v>46082</v>
       </c>
@@ -2026,7 +2086,7 @@
       </c>
     </row>
     <row r="9" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="3">
+      <c r="A9" s="2">
         <v>46113</v>
       </c>
       <c r="B9">
@@ -2034,7 +2094,7 @@
       </c>
     </row>
     <row r="10" spans="1:2" collapsed="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="3">
+      <c r="A10" s="2">
         <f>SUBTOTAL(9,A9:A9)</f>
         <v>46113</v>
       </c>
@@ -2044,7 +2104,7 @@
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="3">
+      <c r="A11" s="2">
         <v>46143</v>
       </c>
       <c r="B11">
@@ -2052,7 +2112,7 @@
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="3">
+      <c r="A12" s="2">
         <f>SUBTOTAL(9,A11:A11)</f>
         <v>46143</v>
       </c>
@@ -2062,7 +2122,7 @@
       </c>
     </row>
     <row r="13" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="3">
+      <c r="A13" s="2">
         <v>46174</v>
       </c>
       <c r="B13">
@@ -2070,7 +2130,7 @@
       </c>
     </row>
     <row r="14" spans="1:2" collapsed="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="3">
+      <c r="A14" s="2">
         <f>SUBTOTAL(9,A13:A13)</f>
         <v>46174</v>
       </c>
@@ -2080,51 +2140,52 @@
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B15" s="3"/>
+      <c r="B15" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC74CA61-C7A0-4E28-B545-0DDC83B696F1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC74CA61-C7A0-4E28-B545-0DDC83B696F1}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8" outlineLevelRow="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="1">
         <v>8000</v>
       </c>
     </row>
-    <row r="3" spans="1:3" collapsed="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="1">
         <v>22000</v>
       </c>
     </row>
@@ -2138,6 +2199,8 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
